--- a/data/metadata/cases_included.xlsx
+++ b/data/metadata/cases_included.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanleyb/The Francis Crick Dropbox/Brian Hanley/HoLSTF_Breast/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hanleyb/Documents/GitHub/VAULT_Breast/data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80129AC-88A4-8A43-84BE-F09FA92A9D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3D9F02-5D4C-A644-8935-340B14C61820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="18880" xr2:uid="{4D5D1DDB-EF31-7A47-BD5A-D5303C8ACDF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>HF004_ET001_D01</t>
   </si>
@@ -81,9 +81,6 @@
   </si>
   <si>
     <t>HF068_ET001_D01</t>
-  </si>
-  <si>
-    <t>HF079_ET001_D01</t>
   </si>
   <si>
     <t>HF083_ET001_D01</t>
@@ -628,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56E43328-03D4-8047-A434-D4370B6CCD1C}">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -976,14 +973,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A115">
-    <sortCondition ref="A38:A115"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A114">
+    <sortCondition ref="A37:A114"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
